--- a/backtest_runs/20260410_193731/by_symbol/EFUL/EFUL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/EFUL/EFUL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-4101.539999999997</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>98313.58</v>
@@ -679,7 +679,7 @@
         <v>-4261.16000000001</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>94052.41999999998</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>94052.41999999998</v>
@@ -817,7 +817,7 @@
         <v>-194.3200000000008</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>93858.09999999999</v>
@@ -1001,7 +1001,7 @@
         <v>-3907.219999999997</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>90124.37999999999</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>90124.37999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-1117.340000000009</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>89270.75999999998</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>89270.75999999998</v>
@@ -1277,7 +1277,7 @@
         <v>-1290.83999999999</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>87979.91999999998</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>87979.91999999998</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>93094.69999999997</v>
@@ -1553,7 +1553,7 @@
         <v>-256.7800000000032</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>92837.91999999997</v>
@@ -1645,7 +1645,7 @@
         <v>-464.9799999999913</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>97119.89999999998</v>
